--- a/public/documents/pieces-reponse-1/R1-cremant-bilan-matiere.xlsx
+++ b/public/documents/pieces-reponse-1/R1-cremant-bilan-matiere.xlsx
@@ -1993,7 +1993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Les doses sont celles que le service applique lui-meme dans son tableau p. 62. Les libelles Kir Princier et VOUIVRE ne figurent pas dans ce tableau : ils sont ajoutes ici, ce qui augmente la consommation reconnue et reduit d'autant l'ecart reproche. Les Kir Bourgogne et Kir Pamplemousse (vin tranquille) sont exclus, comme le service les exclut.</t>
+          <t>Les doses sont celles que le service applique lui-meme dans son tableau p. 62, qui ne compte que six lignes. Trois libelles n'y figurent pas : le Kir Princier, le libelle VOUIVRE et le libelle « Crement / Jura VERRE », le cremant du Jura n'apparaissant chez le service qu'en bouteille de 75 cl. Ils sont ajoutes ici, ce qui augmente la consommation reconnue et reduit d'autant l'ecart reproche. Les Kir Bourgogne et Kir Pamplemousse (vin tranquille) sont exclus, comme le service les exclut.</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
     </row>
